--- a/contoh list import excel.xlsx
+++ b/contoh list import excel.xlsx
@@ -44,112 +44,112 @@
     <t>EMAIL</t>
   </si>
   <si>
-    <t>MB-001</t>
-  </si>
-  <si>
-    <t>Annisa Rahayu</t>
+    <t>MB-030</t>
+  </si>
+  <si>
+    <t>UPIN 1</t>
   </si>
   <si>
     <t>Battery</t>
   </si>
   <si>
-    <t>202410110210345</t>
-  </si>
-  <si>
-    <t>annisa@umm,com</t>
-  </si>
-  <si>
-    <t>MB-002</t>
-  </si>
-  <si>
-    <t>Syaidina Amirul Mukminin</t>
-  </si>
-  <si>
-    <t>202510110210345</t>
-  </si>
-  <si>
-    <t>mukmin@umm,com</t>
-  </si>
-  <si>
-    <t>MB-003</t>
-  </si>
-  <si>
-    <t>Rafelina</t>
+    <t>2024101102103457</t>
+  </si>
+  <si>
+    <t>upin1@gmial.com</t>
+  </si>
+  <si>
+    <t>MB-031</t>
+  </si>
+  <si>
+    <t>UPIN 2</t>
+  </si>
+  <si>
+    <t>2025101102103458</t>
+  </si>
+  <si>
+    <t>upin2@gmial.com</t>
+  </si>
+  <si>
+    <t>MB-032</t>
+  </si>
+  <si>
+    <t>UPIN 3</t>
   </si>
   <si>
     <t>Color Guard</t>
   </si>
   <si>
-    <t>202510210301456</t>
-  </si>
-  <si>
-    <t>rafel@umm,com</t>
-  </si>
-  <si>
-    <t>MB-004</t>
-  </si>
-  <si>
-    <t>Keisha Aqilah Komarudin</t>
+    <t>2025102103014569</t>
+  </si>
+  <si>
+    <t>upin3@gmial.com</t>
+  </si>
+  <si>
+    <t>MB-033</t>
+  </si>
+  <si>
+    <t>UPIN 4</t>
   </si>
   <si>
     <t>Pit Percussion</t>
   </si>
   <si>
-    <t>202510310401567</t>
-  </si>
-  <si>
-    <t>keisha@umm,com</t>
-  </si>
-  <si>
-    <t>MB-005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zainur Riza </t>
+    <t>2025103104015670</t>
+  </si>
+  <si>
+    <t>upin4@gmial.com</t>
+  </si>
+  <si>
+    <t>MB-034</t>
+  </si>
+  <si>
+    <t>UPIN 5</t>
   </si>
   <si>
     <t>Brass</t>
   </si>
   <si>
-    <t>202510410501678</t>
-  </si>
-  <si>
-    <t>riza@umm,com</t>
-  </si>
-  <si>
-    <t>MB-006</t>
-  </si>
-  <si>
-    <t>Siti Talitha Sasha Ulima</t>
-  </si>
-  <si>
-    <t>202510510601789</t>
-  </si>
-  <si>
-    <t>chaca@umm,com</t>
-  </si>
-  <si>
-    <t>MB-007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Naifa Khansa </t>
-  </si>
-  <si>
-    <t>202510610710890</t>
-  </si>
-  <si>
-    <t>nepul@umm,com</t>
-  </si>
-  <si>
-    <t>MB-008</t>
-  </si>
-  <si>
-    <t>Tamam Suhada</t>
-  </si>
-  <si>
-    <t>202510710810901</t>
-  </si>
-  <si>
-    <t>tamam@umm,com</t>
+    <t>2025104105016781</t>
+  </si>
+  <si>
+    <t>upin5@gmial.com</t>
+  </si>
+  <si>
+    <t>MB-035</t>
+  </si>
+  <si>
+    <t>UPIN 6</t>
+  </si>
+  <si>
+    <t>2025105106017892</t>
+  </si>
+  <si>
+    <t>upin6@gmial.com</t>
+  </si>
+  <si>
+    <t>MB-036</t>
+  </si>
+  <si>
+    <t>UPIN 7</t>
+  </si>
+  <si>
+    <t>2025106107108903</t>
+  </si>
+  <si>
+    <t>upin7@gmial.com</t>
+  </si>
+  <si>
+    <t>MB-037</t>
+  </si>
+  <si>
+    <t>UPIN 8</t>
+  </si>
+  <si>
+    <t>2025107108109014</t>
+  </si>
+  <si>
+    <t>upin8@gmial.com</t>
   </si>
 </sst>
 </file>
@@ -162,7 +162,7 @@
     <numFmt numFmtId="178" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="179" formatCode="_-&quot;Rp&quot;* #,##0_-;\-&quot;Rp&quot;* #,##0_-;_-&quot;Rp&quot;* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="23">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -181,13 +181,6 @@
       <u/>
       <sz val="10"/>
       <color rgb="FF800080"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
       <name val="Arial"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -647,150 +640,150 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -799,9 +792,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="1">
@@ -1106,14 +1096,14 @@
       <c r="C2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="4" t="s">
         <v>8</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" ht="12.75" spans="1:5">
+    <row r="3" spans="1:5">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
@@ -1123,7 +1113,7 @@
       <c r="C3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="4" t="s">
         <v>12</v>
       </c>
       <c r="E3" s="3" t="s">
@@ -1134,13 +1124,13 @@
       <c r="A4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="4" t="s">
         <v>17</v>
       </c>
       <c r="E4" s="3" t="s">
@@ -1151,13 +1141,13 @@
       <c r="A5" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="4" t="s">
         <v>22</v>
       </c>
       <c r="E5" s="3" t="s">
@@ -1168,13 +1158,13 @@
       <c r="A6" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="2" t="s">
         <v>25</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="4" t="s">
         <v>27</v>
       </c>
       <c r="E6" s="3" t="s">
@@ -1185,13 +1175,13 @@
       <c r="A7" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E7" s="3" t="s">
@@ -1202,13 +1192,13 @@
       <c r="A8" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="2" t="s">
         <v>34</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="4" t="s">
         <v>35</v>
       </c>
       <c r="E8" s="3" t="s">
@@ -1219,13 +1209,13 @@
       <c r="A9" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="4" t="s">
         <v>39</v>
       </c>
       <c r="E9" s="3" t="s">
@@ -1246,14 +1236,14 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="E2" r:id="rId1" display="annisa@umm,com" tooltip="mailto:annisa@umm,com"/>
-    <hyperlink ref="E3" r:id="rId2" display="mukmin@umm,com" tooltip="mailto:mukmin@umm,com"/>
-    <hyperlink ref="E4" r:id="rId3" display="rafel@umm,com" tooltip="mailto:rafel@umm,com"/>
-    <hyperlink ref="E5" r:id="rId4" display="keisha@umm,com" tooltip="mailto:keisha@umm,com"/>
-    <hyperlink ref="E6" r:id="rId5" display="riza@umm,com" tooltip="mailto:riza@umm,com"/>
-    <hyperlink ref="E7" r:id="rId6" display="chaca@umm,com" tooltip="mailto:chaca@umm,com"/>
-    <hyperlink ref="E8" r:id="rId7" display="nepul@umm,com" tooltip="mailto:nepul@umm,com"/>
-    <hyperlink ref="E9" r:id="rId8" display="tamam@umm,com" tooltip="mailto:tamam@umm,com"/>
+    <hyperlink ref="E8" r:id="rId1" display="upin7@gmial.com" tooltip="mailto:upin1@gmial.com"/>
+    <hyperlink ref="E7" r:id="rId1" display="upin6@gmial.com" tooltip="mailto:upin1@gmial.com"/>
+    <hyperlink ref="E6" r:id="rId1" display="upin5@gmial.com" tooltip="mailto:upin1@gmial.com"/>
+    <hyperlink ref="E5" r:id="rId1" display="upin4@gmial.com" tooltip="mailto:upin1@gmial.com"/>
+    <hyperlink ref="E4" r:id="rId1" display="upin3@gmial.com" tooltip="mailto:upin1@gmial.com"/>
+    <hyperlink ref="E3" r:id="rId1" display="upin2@gmial.com" tooltip="mailto:upin1@gmial.com"/>
+    <hyperlink ref="E2" r:id="rId1" display="upin1@gmial.com" tooltip="mailto:upin1@gmial.com"/>
+    <hyperlink ref="E9" r:id="rId1" display="upin8@gmial.com" tooltip="mailto:upin1@gmial.com"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait"/>
